--- a/task147/golden/housekeeping_block_2027.xlsx
+++ b/task147/golden/housekeeping_block_2027.xlsx
@@ -50,7 +50,7 @@
     <t>Room-nights above capacity: each night's forecast occupied rooms above 380, summed over the roster week's seven nights (HK-04 3.2), to the nearest hundred.</t>
   </si>
   <si>
-    <t>Friday 13 and Saturday 14 August are full on the book (480 rooms); stays booked from today cannot run through them.</t>
+    <t>Friday 13 and Saturday 14 August are full on the book (480 rooms); stays booked from today can run through them only into the rooms those nights' own bookings give back.</t>
   </si>
   <si>
     <t>Last year's season by roster week: departure cleans and stayover services, and the crew's overtime</t>
